--- a/30_table/01_테스트버전/Table_Data_Drop.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Drop.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="192">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -690,6 +690,14 @@
   </si>
   <si>
     <t>item_equip_r_ac_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼 맵 보상 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0028</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5430,7 +5438,27 @@
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C29" s="34"/>
+      <c r="A29" s="32">
+        <v>60027</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="35">
+        <v>100</v>
+      </c>
+      <c r="E29" s="35">
+        <v>0</v>
+      </c>
+      <c r="F29" s="35">
+        <v>0</v>
+      </c>
+      <c r="G29" s="35">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C30" s="34"/>

--- a/30_table/01_테스트버전/Table_Data_Drop.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Drop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="105" windowWidth="19215" windowHeight="12075" activeTab="2"/>
+    <workbookView xWindow="-15" yWindow="165" windowWidth="19215" windowHeight="12015" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DOC History" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="232">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -376,329 +376,473 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>튜토리얼 맵 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0008</t>
+  </si>
+  <si>
+    <t>drop_0009</t>
+  </si>
+  <si>
+    <t>drop_0010</t>
+  </si>
+  <si>
+    <t>drop_0011</t>
+  </si>
+  <si>
+    <t>drop_0012</t>
+  </si>
+  <si>
+    <t>drop_0013</t>
+  </si>
+  <si>
+    <t>drop_0014</t>
+  </si>
+  <si>
+    <t>drop_0015</t>
+  </si>
+  <si>
+    <t>drop_0016</t>
+  </si>
+  <si>
+    <t>drop_0017</t>
+  </si>
+  <si>
+    <t>drop_0018</t>
+  </si>
+  <si>
+    <t>drop_0019</t>
+  </si>
+  <si>
+    <t>drop_0020</t>
+  </si>
+  <si>
+    <t>D등급 맵 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C등급 맵 보상</t>
+  </si>
+  <si>
+    <t>B등급 맵 보상</t>
+  </si>
+  <si>
+    <t>A등급 맵 보상</t>
+  </si>
+  <si>
+    <t>drop_0022</t>
+  </si>
+  <si>
+    <t>D등급 맵 실버 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D등급 맵 골드 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C등급 맵 실버 보상</t>
+  </si>
+  <si>
+    <t>C등급 맵 골드 보상</t>
+  </si>
+  <si>
+    <t>B등급 맵 실버 보상</t>
+  </si>
+  <si>
+    <t>B등급 맵 골드 보상</t>
+  </si>
+  <si>
+    <t>A등급 맵 실버 보상</t>
+  </si>
+  <si>
+    <t>A등급 맵 골드 보상</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_02</t>
+  </si>
+  <si>
+    <t>item_potion_heal_01</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_05</t>
+  </si>
+  <si>
+    <t>item_equip_n_ac_02</t>
+  </si>
+  <si>
+    <t>item_equip_n_bo_02</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_02</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_05</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_08</t>
+  </si>
+  <si>
+    <t>item_potion_heal_02</t>
+  </si>
+  <si>
+    <t>item_equip_n_ac_05</t>
+  </si>
+  <si>
+    <t>item_equip_n_bo_05</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_08</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_11</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_11</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_14</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_17</t>
+  </si>
+  <si>
+    <t>item_potion_heal_03</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_14</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_17</t>
+  </si>
+  <si>
+    <t>item_equip_n_ac_08</t>
+  </si>
+  <si>
+    <t>item_equip_n_bo_08</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_20</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_23</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_26</t>
+  </si>
+  <si>
+    <t>item_potion_heal_04</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_20</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_23</t>
+  </si>
+  <si>
+    <t>item_equip_n_ac_11</t>
+  </si>
+  <si>
+    <t>item_equip_n_bo_11</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_29</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_32</t>
+  </si>
+  <si>
+    <t>item_equip_n_we_35</t>
+  </si>
+  <si>
+    <t>슬라임 드롭 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ar_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ar_07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ac_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_bo_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_we_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_we_07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_we_10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>킹슬라임 드롭 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션 무기상자 01 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션 갑옷상자 01 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0023</t>
+  </si>
+  <si>
+    <t>drop_0024</t>
+  </si>
+  <si>
+    <t>미션 갑옷상자 02 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0025</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ac_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_bo_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0026</t>
+  </si>
+  <si>
+    <t>출석 보상 영웅 소환권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_summon_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_summon_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_summon_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_summon_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_summon_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조르의 보석함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_r_ac_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_r_ac_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_r_ac_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_r_ac_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_r_ac_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼 맵 보상 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리비히의 서 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0029</t>
+  </si>
+  <si>
+    <t>좀비 드롭 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박쥐 드롭 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구울 드롭 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서큐버스 드롭 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0030</t>
+  </si>
+  <si>
+    <t>drop_0031</t>
+  </si>
+  <si>
+    <t>drop_0032</t>
+  </si>
+  <si>
+    <t>drop_0033</t>
+  </si>
+  <si>
+    <t>item_quest_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_quest_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갈색 늑대 드롭 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회색 늑대 드롭 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0034</t>
+  </si>
+  <si>
+    <t>drop_0035</t>
+  </si>
+  <si>
+    <t>drop_0036</t>
+  </si>
+  <si>
+    <t>drop_0037</t>
+  </si>
+  <si>
+    <t>drop_0038</t>
+  </si>
+  <si>
+    <t>item_equip_n_ar_16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ar_19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_bo_10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ar_10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ar_13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_bo_07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ac_10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ac_07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_we_22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_we_13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_we_25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_we_16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_we_28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_we_19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C등급 보물상자 드롭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B등급 보물상자 드롭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A등급 보물상자 드롭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ac_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ac_08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ac_11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>drop_0007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보물상자 드롭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>튜토리얼 맵 보상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_0008</t>
-  </si>
-  <si>
-    <t>drop_0009</t>
-  </si>
-  <si>
-    <t>drop_0010</t>
-  </si>
-  <si>
-    <t>drop_0011</t>
-  </si>
-  <si>
-    <t>drop_0012</t>
-  </si>
-  <si>
-    <t>drop_0013</t>
-  </si>
-  <si>
-    <t>drop_0014</t>
-  </si>
-  <si>
-    <t>drop_0015</t>
-  </si>
-  <si>
-    <t>drop_0016</t>
-  </si>
-  <si>
-    <t>drop_0017</t>
-  </si>
-  <si>
-    <t>drop_0018</t>
-  </si>
-  <si>
-    <t>drop_0019</t>
-  </si>
-  <si>
-    <t>drop_0020</t>
-  </si>
-  <si>
-    <t>D등급 맵 보상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C등급 맵 보상</t>
-  </si>
-  <si>
-    <t>B등급 맵 보상</t>
-  </si>
-  <si>
-    <t>A등급 맵 보상</t>
-  </si>
-  <si>
-    <t>drop_0022</t>
-  </si>
-  <si>
-    <t>D등급 맵 실버 보상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D등급 맵 골드 보상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C등급 맵 실버 보상</t>
-  </si>
-  <si>
-    <t>C등급 맵 골드 보상</t>
-  </si>
-  <si>
-    <t>B등급 맵 실버 보상</t>
-  </si>
-  <si>
-    <t>B등급 맵 골드 보상</t>
-  </si>
-  <si>
-    <t>A등급 맵 실버 보상</t>
-  </si>
-  <si>
-    <t>A등급 맵 골드 보상</t>
-  </si>
-  <si>
-    <t>item_equip_n_ar_02</t>
-  </si>
-  <si>
-    <t>item_potion_heal_01</t>
-  </si>
-  <si>
-    <t>item_equip_n_ar_05</t>
-  </si>
-  <si>
-    <t>item_equip_n_ac_02</t>
-  </si>
-  <si>
-    <t>item_equip_n_bo_02</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_02</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_05</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_08</t>
-  </si>
-  <si>
-    <t>item_potion_heal_02</t>
-  </si>
-  <si>
-    <t>item_equip_n_ac_05</t>
-  </si>
-  <si>
-    <t>item_equip_n_bo_05</t>
-  </si>
-  <si>
-    <t>item_equip_n_ar_08</t>
-  </si>
-  <si>
-    <t>item_equip_n_ar_11</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_11</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_14</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_17</t>
-  </si>
-  <si>
-    <t>item_potion_heal_03</t>
-  </si>
-  <si>
-    <t>item_equip_n_ar_14</t>
-  </si>
-  <si>
-    <t>item_equip_n_ar_17</t>
-  </si>
-  <si>
-    <t>item_equip_n_ac_08</t>
-  </si>
-  <si>
-    <t>item_equip_n_bo_08</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_20</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_23</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_26</t>
-  </si>
-  <si>
-    <t>item_potion_heal_04</t>
-  </si>
-  <si>
-    <t>item_equip_n_ar_20</t>
-  </si>
-  <si>
-    <t>item_equip_n_ar_23</t>
-  </si>
-  <si>
-    <t>item_equip_n_ac_11</t>
-  </si>
-  <si>
-    <t>item_equip_n_bo_11</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_29</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_32</t>
-  </si>
-  <si>
-    <t>item_equip_n_we_35</t>
-  </si>
-  <si>
-    <t>슬라임 드롭 보상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_ar_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_ar_07</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_ac_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_bo_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_we_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_we_07</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_we_10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>킹슬라임 드롭 보상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>drop_0021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미션 무기상자 01 보상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미션 갑옷상자 01 보상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_0023</t>
-  </si>
-  <si>
-    <t>drop_0024</t>
-  </si>
-  <si>
-    <t>미션 갑옷상자 02 보상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_0025</t>
-  </si>
-  <si>
-    <t>item_equip_n_ar_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_ac_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_bo_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_0026</t>
-  </si>
-  <si>
-    <t>출석 보상 영웅 소환권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_summon_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_summon_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_summon_03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_summon_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_summon_05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조르의 보석함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>drop_0027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_r_ac_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_r_ac_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_r_ac_03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_r_ac_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_r_ac_05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>튜토리얼 맵 보상 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>drop_0028</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0039</t>
+  </si>
+  <si>
+    <t>drop_0040</t>
   </si>
 </sst>
 </file>
@@ -4300,7 +4444,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="35" bestFit="1" customWidth="1"/>
@@ -4587,10 +4731,10 @@
         <v>60006</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="D8" s="35">
         <v>100</v>
@@ -4603,6 +4747,18 @@
       </c>
       <c r="G8" s="35">
         <v>0</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" s="35">
+        <v>3000</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="K8" s="35">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
@@ -4610,10 +4766,10 @@
         <v>60007</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D9" s="35">
         <v>100</v>
@@ -4628,19 +4784,19 @@
         <v>0</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I9" s="35">
         <v>2000</v>
       </c>
       <c r="J9" s="35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K9" s="35">
         <v>2000</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M9" s="35">
         <v>2000</v>
@@ -4651,10 +4807,10 @@
         <v>60008</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D10" s="35">
         <v>576</v>
@@ -4667,6 +4823,12 @@
       </c>
       <c r="G10" s="35">
         <v>0</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="I10" s="35">
+        <v>3000</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
@@ -4674,10 +4836,10 @@
         <v>60009</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D11" s="35">
         <v>0</v>
@@ -4692,31 +4854,31 @@
         <v>0</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I11" s="35">
         <v>6000</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K11" s="35">
         <v>100</v>
       </c>
       <c r="L11" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M11" s="35">
         <v>100</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O11" s="35">
         <v>100</v>
       </c>
       <c r="P11" s="35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q11" s="35">
         <v>100</v>
@@ -4727,10 +4889,10 @@
         <v>60010</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" s="35">
         <v>0</v>
@@ -4745,19 +4907,19 @@
         <v>0</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I12" s="35">
         <v>300</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K12" s="35">
         <v>300</v>
       </c>
       <c r="L12" s="35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M12" s="35">
         <v>300</v>
@@ -4768,10 +4930,10 @@
         <v>60011</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D13" s="35">
         <v>672</v>
@@ -4784,6 +4946,12 @@
       </c>
       <c r="G13" s="35">
         <v>0</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" s="35">
+        <v>3000</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
@@ -4791,10 +4959,10 @@
         <v>60012</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D14" s="35">
         <v>0</v>
@@ -4809,31 +4977,31 @@
         <v>0</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I14" s="35">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K14" s="35">
         <v>100</v>
       </c>
       <c r="L14" s="35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M14" s="35">
         <v>100</v>
       </c>
       <c r="N14" s="35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O14" s="35">
         <v>100</v>
       </c>
       <c r="P14" s="35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q14" s="35">
         <v>100</v>
@@ -4844,10 +5012,10 @@
         <v>60013</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D15" s="35">
         <v>0</v>
@@ -4862,19 +5030,19 @@
         <v>0</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I15" s="35">
         <v>200</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K15" s="35">
         <v>200</v>
       </c>
       <c r="L15" s="35" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M15" s="35">
         <v>200</v>
@@ -4885,10 +5053,10 @@
         <v>60014</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D16" s="35">
         <v>768</v>
@@ -4901,6 +5069,12 @@
       </c>
       <c r="G16" s="35">
         <v>0</v>
+      </c>
+      <c r="H16" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="35">
+        <v>3000</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
@@ -4908,10 +5082,10 @@
         <v>60015</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D17" s="35">
         <v>0</v>
@@ -4926,31 +5100,31 @@
         <v>0</v>
       </c>
       <c r="H17" s="35" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I17" s="35">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="J17" s="35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K17" s="35">
         <v>50</v>
       </c>
       <c r="L17" s="35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M17" s="35">
         <v>50</v>
       </c>
       <c r="N17" s="35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O17" s="35">
         <v>50</v>
       </c>
       <c r="P17" s="35" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Q17" s="35">
         <v>50</v>
@@ -4961,10 +5135,10 @@
         <v>60016</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D18" s="35">
         <v>0</v>
@@ -4979,19 +5153,19 @@
         <v>0</v>
       </c>
       <c r="H18" s="35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I18" s="35">
         <v>100</v>
       </c>
       <c r="J18" s="35" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K18" s="35">
         <v>100</v>
       </c>
       <c r="L18" s="35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M18" s="35">
         <v>100</v>
@@ -5002,10 +5176,10 @@
         <v>60017</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D19" s="35">
         <v>864</v>
@@ -5018,6 +5192,12 @@
       </c>
       <c r="G19" s="35">
         <v>0</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="35">
+        <v>3000</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
@@ -5025,10 +5205,10 @@
         <v>60018</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D20" s="35">
         <v>0</v>
@@ -5043,31 +5223,31 @@
         <v>0</v>
       </c>
       <c r="H20" s="35" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I20" s="35">
-        <v>2500</v>
+        <v>6000</v>
       </c>
       <c r="J20" s="35" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K20" s="35">
         <v>50</v>
       </c>
       <c r="L20" s="35" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M20" s="35">
         <v>50</v>
       </c>
       <c r="N20" s="35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O20" s="35">
         <v>50</v>
       </c>
       <c r="P20" s="35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Q20" s="35">
         <v>50</v>
@@ -5078,10 +5258,10 @@
         <v>60019</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" s="35">
         <v>0</v>
@@ -5096,19 +5276,19 @@
         <v>0</v>
       </c>
       <c r="H21" s="35" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I21" s="35">
         <v>50</v>
       </c>
       <c r="J21" s="35" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K21" s="35">
         <v>50</v>
       </c>
       <c r="L21" s="35" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M21" s="35">
         <v>50</v>
@@ -5119,10 +5299,10 @@
         <v>60020</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="D22" s="35">
         <v>0</v>
@@ -5137,43 +5317,43 @@
         <v>0</v>
       </c>
       <c r="H22" s="35" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I22" s="35">
         <v>50</v>
       </c>
       <c r="J22" s="35" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K22" s="35">
         <v>50</v>
       </c>
       <c r="L22" s="35" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M22" s="35">
         <v>50</v>
       </c>
       <c r="N22" s="35" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O22" s="35">
         <v>50</v>
       </c>
       <c r="P22" s="35" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q22" s="35">
         <v>50</v>
       </c>
       <c r="R22" s="35" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="S22" s="35">
         <v>50</v>
       </c>
       <c r="T22" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="U22" s="35">
         <v>50</v>
@@ -5184,10 +5364,10 @@
         <v>60021</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D23" s="35">
         <v>0</v>
@@ -5202,19 +5382,19 @@
         <v>0</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I23" s="35">
         <v>100</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K23" s="35">
         <v>100</v>
       </c>
       <c r="L23" s="35" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M23" s="35">
         <v>100</v>
@@ -5225,10 +5405,10 @@
         <v>60022</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D24" s="35">
         <v>0</v>
@@ -5243,19 +5423,19 @@
         <v>0</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I24" s="35">
         <v>3500</v>
       </c>
       <c r="J24" s="35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K24" s="35">
         <v>3500</v>
       </c>
       <c r="L24" s="35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M24" s="35">
         <v>3000</v>
@@ -5266,10 +5446,10 @@
         <v>60023</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D25" s="35">
         <v>0</v>
@@ -5284,13 +5464,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I25" s="35">
         <v>5000</v>
       </c>
       <c r="J25" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K25" s="35">
         <v>5000</v>
@@ -5301,10 +5481,10 @@
         <v>60024</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D26" s="35">
         <v>0</v>
@@ -5319,13 +5499,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I26" s="35">
         <v>5000</v>
       </c>
       <c r="J26" s="35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K26" s="35">
         <v>5000</v>
@@ -5336,10 +5516,10 @@
         <v>60025</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D27" s="35">
         <v>0</v>
@@ -5354,31 +5534,31 @@
         <v>0</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I27" s="35">
         <v>2000</v>
       </c>
       <c r="J27" s="35" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K27" s="35">
         <v>2000</v>
       </c>
       <c r="L27" s="35" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M27" s="35">
         <v>2000</v>
       </c>
       <c r="N27" s="35" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O27" s="35">
         <v>2000</v>
       </c>
       <c r="P27" s="35" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q27" s="35">
         <v>2000</v>
@@ -5389,10 +5569,10 @@
         <v>60026</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="D28" s="35">
         <v>0</v>
@@ -5407,31 +5587,31 @@
         <v>0</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I28" s="35">
         <v>2000</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K28" s="35">
         <v>2000</v>
       </c>
       <c r="L28" s="35" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M28" s="35">
         <v>2000</v>
       </c>
       <c r="N28" s="35" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="O28" s="35">
         <v>2000</v>
       </c>
       <c r="P28" s="35" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Q28" s="35">
         <v>2000</v>
@@ -5442,10 +5622,10 @@
         <v>60027</v>
       </c>
       <c r="B29" s="35" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D29" s="35">
         <v>100</v>
@@ -5461,52 +5641,442 @@
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C30" s="34"/>
+      <c r="A30" s="32">
+        <v>60028</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="35">
+        <v>0</v>
+      </c>
+      <c r="E30" s="35">
+        <v>0</v>
+      </c>
+      <c r="F30" s="35">
+        <v>0</v>
+      </c>
+      <c r="G30" s="35">
+        <v>0</v>
+      </c>
+      <c r="H30" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="I30" s="35">
+        <v>10000</v>
+      </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C31" s="34"/>
+      <c r="A31" s="32">
+        <v>60029</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="35">
+        <v>0</v>
+      </c>
+      <c r="E31" s="35">
+        <v>0</v>
+      </c>
+      <c r="F31" s="35">
+        <v>0</v>
+      </c>
+      <c r="G31" s="35">
+        <v>0</v>
+      </c>
+      <c r="H31" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="I31" s="35">
+        <v>100</v>
+      </c>
+      <c r="J31" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="K31" s="35">
+        <v>100</v>
+      </c>
+      <c r="L31" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="M31" s="35">
+        <v>100</v>
+      </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C32" s="34"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C33" s="34"/>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C34" s="34"/>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C35" s="34"/>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C36" s="34"/>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C37" s="34"/>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C38" s="34"/>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C39" s="34"/>
-    </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C40" s="34"/>
-    </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C41" s="34"/>
-    </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="32">
+        <v>60030</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="D32" s="35">
+        <v>0</v>
+      </c>
+      <c r="E32" s="35">
+        <v>0</v>
+      </c>
+      <c r="F32" s="35">
+        <v>0</v>
+      </c>
+      <c r="G32" s="35">
+        <v>0</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="I32" s="35">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="32">
+        <v>60031</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="35">
+        <v>0</v>
+      </c>
+      <c r="E33" s="35">
+        <v>0</v>
+      </c>
+      <c r="F33" s="35">
+        <v>0</v>
+      </c>
+      <c r="G33" s="35">
+        <v>0</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="I33" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="32">
+        <v>60032</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="35">
+        <v>0</v>
+      </c>
+      <c r="E34" s="35">
+        <v>0</v>
+      </c>
+      <c r="F34" s="35">
+        <v>0</v>
+      </c>
+      <c r="G34" s="35">
+        <v>0</v>
+      </c>
+      <c r="H34" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="I34" s="35">
+        <v>100</v>
+      </c>
+      <c r="J34" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="K34" s="35">
+        <v>100</v>
+      </c>
+      <c r="L34" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="M34" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="32">
+        <v>60033</v>
+      </c>
+      <c r="B35" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" s="35">
+        <v>0</v>
+      </c>
+      <c r="E35" s="35">
+        <v>0</v>
+      </c>
+      <c r="F35" s="35">
+        <v>0</v>
+      </c>
+      <c r="G35" s="35">
+        <v>0</v>
+      </c>
+      <c r="H35" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="I35" s="35">
+        <v>100</v>
+      </c>
+      <c r="J35" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="K35" s="35">
+        <v>100</v>
+      </c>
+      <c r="L35" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="M35" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="32">
+        <v>60034</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" s="35">
+        <v>0</v>
+      </c>
+      <c r="E36" s="35">
+        <v>0</v>
+      </c>
+      <c r="F36" s="35">
+        <v>0</v>
+      </c>
+      <c r="G36" s="35">
+        <v>0</v>
+      </c>
+      <c r="H36" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="I36" s="35">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="32">
+        <v>60035</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="D37" s="35">
+        <v>0</v>
+      </c>
+      <c r="E37" s="35">
+        <v>0</v>
+      </c>
+      <c r="F37" s="35">
+        <v>0</v>
+      </c>
+      <c r="G37" s="35">
+        <v>0</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="I37" s="35">
+        <v>100</v>
+      </c>
+      <c r="J37" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="K37" s="35">
+        <v>100</v>
+      </c>
+      <c r="L37" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="M37" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="32">
+        <v>60036</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="D38" s="35">
+        <v>0</v>
+      </c>
+      <c r="E38" s="35">
+        <v>0</v>
+      </c>
+      <c r="F38" s="35">
+        <v>0</v>
+      </c>
+      <c r="G38" s="35">
+        <v>0</v>
+      </c>
+      <c r="H38" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="I38" s="35">
+        <v>100</v>
+      </c>
+      <c r="J38" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="K38" s="35">
+        <v>100</v>
+      </c>
+      <c r="L38" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="M38" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="32">
+        <v>60037</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="D39" s="35">
+        <v>0</v>
+      </c>
+      <c r="E39" s="35">
+        <v>0</v>
+      </c>
+      <c r="F39" s="35">
+        <v>0</v>
+      </c>
+      <c r="G39" s="35">
+        <v>0</v>
+      </c>
+      <c r="H39" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="I39" s="35">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="32">
+        <v>60038</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="D40" s="35">
+        <v>150</v>
+      </c>
+      <c r="E40" s="35">
+        <v>2000</v>
+      </c>
+      <c r="F40" s="35">
+        <v>0</v>
+      </c>
+      <c r="G40" s="35">
+        <v>0</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="I40" s="35">
+        <v>3000</v>
+      </c>
+      <c r="J40" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="K40" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="32">
+        <v>60039</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="D41" s="35">
+        <v>200</v>
+      </c>
+      <c r="E41" s="35">
+        <v>2500</v>
+      </c>
+      <c r="F41" s="35">
+        <v>0</v>
+      </c>
+      <c r="G41" s="35">
+        <v>0</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="I41" s="35">
+        <v>3000</v>
+      </c>
+      <c r="J41" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="K41" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C42" s="34"/>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C43" s="34"/>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C44" s="34"/>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C45" s="34"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C46" s="34"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C47" s="34"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>

--- a/30_table/01_테스트버전/Table_Data_Drop.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Drop.xlsx
@@ -5736,7 +5736,7 @@
         <v>197</v>
       </c>
       <c r="I32" s="35">
-        <v>2000</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
